--- a/data/trans_dic/P25A$voluntad-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25A$voluntad-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,84; 73,13</t>
+          <t>44,93; 72,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,29; 85,93</t>
+          <t>66,52; 85,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66,11; 84,8</t>
+          <t>65,08; 84,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43,56; 89,22</t>
+          <t>46,51; 89,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,18; 91,54</t>
+          <t>64,04; 91,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,66; 84,67</t>
+          <t>59,27; 83,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,7; 74,54</t>
+          <t>50,64; 73,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,65; 85,32</t>
+          <t>69,57; 84,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,74; 82,07</t>
+          <t>66,64; 82,19</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>46,9; 65,03</t>
+          <t>46,81; 65,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,56; 76,09</t>
+          <t>57,42; 75,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,74; 68,38</t>
+          <t>41,45; 66,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,92; 80,36</t>
+          <t>41,04; 77,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>75,53; 94,31</t>
+          <t>75,6; 93,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,93; 89,38</t>
+          <t>54,0; 89,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,21; 65,57</t>
+          <t>48,54; 64,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>66,25; 80,46</t>
+          <t>65,83; 80,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51,26; 70,46</t>
+          <t>52,57; 71,01</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,79; 74,14</t>
+          <t>50,27; 74,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,15; 79,8</t>
+          <t>60,56; 79,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,8; 65,52</t>
+          <t>41,84; 67,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,76; 93,74</t>
+          <t>51,7; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,52; 89,23</t>
+          <t>56,35; 88,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,82; 86,19</t>
+          <t>51,75; 86,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,4; 76,76</t>
+          <t>54,62; 75,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>62,79; 80,03</t>
+          <t>63,39; 79,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48,96; 69,55</t>
+          <t>48,46; 69,17</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>53,12; 74,68</t>
+          <t>52,64; 75,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,51; 79,46</t>
+          <t>60,85; 79,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,08; 68,14</t>
+          <t>48,24; 68,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,67; 75,6</t>
+          <t>43,42; 75,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,75; 93,55</t>
+          <t>72,28; 93,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,02; 73,61</t>
+          <t>44,14; 73,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,08; 70,89</t>
+          <t>53,89; 71,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>67,17; 81,94</t>
+          <t>67,49; 81,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,99; 66,88</t>
+          <t>49,44; 66,89</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>67,02; 90,11</t>
+          <t>66,87; 90,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,11; 84,8</t>
+          <t>57,99; 84,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42,31; 77,75</t>
+          <t>40,43; 76,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73,93; 96,89</t>
+          <t>71,61; 96,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,69; 85,14</t>
+          <t>48,07; 84,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,0; 67,32</t>
+          <t>20,65; 67,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,55; 92,02</t>
+          <t>74,91; 91,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60,16; 82,3</t>
+          <t>59,89; 81,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40,92; 67,33</t>
+          <t>40,3; 68,53</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,64; 56,75</t>
+          <t>30,23; 58,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61,51; 80,96</t>
+          <t>59,87; 80,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55,29; 83,29</t>
+          <t>57,13; 83,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27,69; 77,03</t>
+          <t>27,12; 77,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59,56; 95,35</t>
+          <t>53,69; 95,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61,2; 100,0</t>
+          <t>61,37; 95,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,09; 57,78</t>
+          <t>34,86; 57,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64,76; 82,19</t>
+          <t>64,25; 82,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62,88; 84,92</t>
+          <t>62,1; 83,89</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>47,25; 67,82</t>
+          <t>46,8; 67,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>60,1; 75,76</t>
+          <t>59,75; 75,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33,74; 52,32</t>
+          <t>33,89; 51,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38,29; 73,28</t>
+          <t>38,72; 73,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>65,59; 83,61</t>
+          <t>64,13; 83,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,28; 75,98</t>
+          <t>55,23; 76,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,48; 65,39</t>
+          <t>48,34; 65,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>64,45; 76,14</t>
+          <t>64,69; 76,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44,74; 58,85</t>
+          <t>45,02; 59,32</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41,4; 58,61</t>
+          <t>41,33; 58,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41,07; 60,05</t>
+          <t>40,79; 59,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64,82; 82,31</t>
+          <t>64,44; 81,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53,42; 75,91</t>
+          <t>53,34; 76,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>56,31; 79,05</t>
+          <t>57,09; 79,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,24; 88,28</t>
+          <t>66,29; 87,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,84; 62,4</t>
+          <t>48,16; 61,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,43; 63,94</t>
+          <t>49,76; 64,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>68,74; 82,01</t>
+          <t>68,62; 82,65</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>53,55; 61,28</t>
+          <t>53,56; 61,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64,17; 70,85</t>
+          <t>63,84; 70,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56,39; 64,1</t>
+          <t>56,27; 64,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59,98; 72,58</t>
+          <t>60,04; 72,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>72,9; 81,84</t>
+          <t>72,97; 81,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>64,35; 74,91</t>
+          <t>64,57; 74,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>56,52; 63,28</t>
+          <t>56,57; 63,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>67,85; 73,29</t>
+          <t>67,77; 73,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>60,47; 66,96</t>
+          <t>60,43; 66,62</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21291; 33970</t>
+          <t>20870; 33480</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53758; 69692</t>
+          <t>53948; 69120</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52197; 66957</t>
+          <t>51385; 66506</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8743; 17908</t>
+          <t>9337; 17941</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25691; 36647</t>
+          <t>25637; 36823</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31012; 44010</t>
+          <t>30807; 43626</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34393; 49588</t>
+          <t>33689; 48742</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84363; 103353</t>
+          <t>84271; 102872</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>87392; 107468</t>
+          <t>87260; 107624</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53391; 74040</t>
+          <t>53296; 74782</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70828; 92023</t>
+          <t>69449; 91564</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31637; 49455</t>
+          <t>29983; 47997</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10838; 20777</t>
+          <t>10611; 19994</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45176; 56412</t>
+          <t>45222; 55877</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16676; 26181</t>
+          <t>15819; 26094</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68748; 91598</t>
+          <t>67809; 90367</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>119758; 145430</t>
+          <t>118994; 145570</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52089; 71600</t>
+          <t>53424; 72157</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31737; 47255</t>
+          <t>32042; 47372</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49507; 65676</t>
+          <t>49846; 65431</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25917; 40629</t>
+          <t>25943; 41756</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7510; 13345</t>
+          <t>7359; 14236</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18854; 29251</t>
+          <t>18471; 28964</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14306; 23796</t>
+          <t>14288; 23839</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43195; 59854</t>
+          <t>42587; 59235</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>72264; 92104</t>
+          <t>72946; 91998</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>43876; 62329</t>
+          <t>43428; 61987</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40304; 56665</t>
+          <t>39943; 56921</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64855; 83777</t>
+          <t>64158; 83812</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40135; 59342</t>
+          <t>42013; 59758</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17209; 28487</t>
+          <t>16361; 28588</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33822; 43492</t>
+          <t>33604; 43631</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19213; 32878</t>
+          <t>19715; 32892</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60278; 80504</t>
+          <t>61197; 80777</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>102053; 124492</t>
+          <t>102544; 124161</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64554; 88123</t>
+          <t>65140; 88137</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>27553; 37044</t>
+          <t>27493; 37068</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29299; 42758</t>
+          <t>29242; 42844</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13424; 24667</t>
+          <t>12826; 24248</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21459; 28126</t>
+          <t>20786; 28133</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13344; 22863</t>
+          <t>12907; 22768</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3589; 11502</t>
+          <t>3528; 11575</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>52993; 64545</t>
+          <t>52539; 64179</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>46492; 63594</t>
+          <t>46282; 63077</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19973; 32867</t>
+          <t>19670; 33452</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15670; 30005</t>
+          <t>15982; 30702</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51126; 67291</t>
+          <t>49761; 66567</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24534; 36959</t>
+          <t>25351; 37014</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5209; 14491</t>
+          <t>5102; 14513</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13014; 20832</t>
+          <t>11732; 20824</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10281; 16800</t>
+          <t>10311; 15989</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24435; 41421</t>
+          <t>24986; 41544</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>67976; 86268</t>
+          <t>67436; 86248</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38465; 51948</t>
+          <t>37990; 51319</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>43548; 62502</t>
+          <t>43130; 62154</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>97681; 123133</t>
+          <t>97112; 122346</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42816; 66400</t>
+          <t>43005; 65170</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12585; 24088</t>
+          <t>12727; 24038</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>60222; 76769</t>
+          <t>58880; 76666</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>46673; 64153</t>
+          <t>46631; 64206</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>60616; 81759</t>
+          <t>60440; 82243</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>163923; 193648</t>
+          <t>164542; 194136</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>94550; 124368</t>
+          <t>95157; 125361</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>57349; 81186</t>
+          <t>57247; 81192</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>53480; 78205</t>
+          <t>53123; 77907</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>66180; 84035</t>
+          <t>65796; 83245</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>38562; 54791</t>
+          <t>38499; 55282</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>37688; 52906</t>
+          <t>38207; 53457</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>42998; 56451</t>
+          <t>42389; 56134</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>102898; 131482</t>
+          <t>101479; 130363</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>97460; 126053</t>
+          <t>98108; 127528</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>114131; 136167</t>
+          <t>113937; 137232</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>334485; 382759</t>
+          <t>334505; 382484</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>523706; 578177</t>
+          <t>520980; 577329</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>341428; 388135</t>
+          <t>340682; 387723</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>150391; 181985</t>
+          <t>150536; 181390</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>281802; 316349</t>
+          <t>282067; 314939</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>216088; 251543</t>
+          <t>216823; 250636</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>494708; 553869</t>
+          <t>495184; 552332</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>816026; 881413</t>
+          <t>815047; 880525</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>569218; 630305</t>
+          <t>568845; 627130</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$voluntad-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25A$voluntad-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,93; 72,08</t>
+          <t>45,57; 72,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,52; 85,23</t>
+          <t>67,08; 85,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,08; 84,23</t>
+          <t>64,36; 84,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46,51; 89,38</t>
+          <t>43,73; 88,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,04; 91,98</t>
+          <t>63,65; 91,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,27; 83,93</t>
+          <t>60,2; 85,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,64; 73,27</t>
+          <t>50,05; 73,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,57; 84,92</t>
+          <t>69,62; 85,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,64; 82,19</t>
+          <t>66,63; 81,67</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>46,81; 65,69</t>
+          <t>46,34; 65,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,42; 75,71</t>
+          <t>56,73; 75,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,45; 66,36</t>
+          <t>44,22; 67,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,04; 77,33</t>
+          <t>37,8; 77,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>75,6; 93,42</t>
+          <t>75,18; 93,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,0; 89,08</t>
+          <t>56,91; 89,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,54; 64,69</t>
+          <t>48,91; 65,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>65,83; 80,53</t>
+          <t>65,47; 79,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,57; 71,01</t>
+          <t>50,79; 70,59</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50,27; 74,32</t>
+          <t>50,35; 74,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,56; 79,5</t>
+          <t>59,54; 80,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,84; 67,34</t>
+          <t>40,74; 65,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,7; 100,0</t>
+          <t>51,28; 93,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,35; 88,36</t>
+          <t>57,48; 88,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,75; 86,35</t>
+          <t>56,49; 86,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,62; 75,97</t>
+          <t>53,59; 75,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63,39; 79,94</t>
+          <t>61,99; 80,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48,46; 69,17</t>
+          <t>50,4; 68,36</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,64; 75,01</t>
+          <t>52,1; 73,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,85; 79,49</t>
+          <t>61,45; 80,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,24; 68,61</t>
+          <t>47,22; 68,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,42; 75,87</t>
+          <t>45,61; 76,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,28; 93,85</t>
+          <t>71,69; 93,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,14; 73,64</t>
+          <t>44,22; 73,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,89; 71,13</t>
+          <t>54,03; 72,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>67,49; 81,72</t>
+          <t>67,45; 81,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49,44; 66,89</t>
+          <t>50,23; 66,74</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,87; 90,17</t>
+          <t>66,97; 90,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57,99; 84,97</t>
+          <t>59,35; 86,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,43; 76,43</t>
+          <t>42,3; 77,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71,61; 96,92</t>
+          <t>74,42; 96,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,07; 84,79</t>
+          <t>50,22; 84,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,65; 67,75</t>
+          <t>20,81; 68,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,91; 91,5</t>
+          <t>73,77; 91,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>59,89; 81,63</t>
+          <t>59,95; 82,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40,3; 68,53</t>
+          <t>39,3; 67,36</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30,23; 58,07</t>
+          <t>28,5; 56,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59,87; 80,09</t>
+          <t>61,21; 81,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57,13; 83,41</t>
+          <t>55,78; 82,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27,12; 77,15</t>
+          <t>32,17; 77,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53,69; 95,31</t>
+          <t>58,41; 95,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61,37; 95,17</t>
+          <t>60,69; 100,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,86; 57,96</t>
+          <t>34,89; 57,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64,25; 82,17</t>
+          <t>64,85; 82,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62,1; 83,89</t>
+          <t>62,38; 83,85</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,8; 67,44</t>
+          <t>46,88; 66,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>59,75; 75,28</t>
+          <t>59,65; 75,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33,89; 51,35</t>
+          <t>33,97; 51,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38,72; 73,13</t>
+          <t>39,17; 73,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>64,13; 83,5</t>
+          <t>64,44; 82,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,23; 76,04</t>
+          <t>54,9; 75,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,34; 65,78</t>
+          <t>47,81; 65,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>64,69; 76,33</t>
+          <t>64,25; 76,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45,02; 59,32</t>
+          <t>44,53; 58,95</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41,33; 58,62</t>
+          <t>42,05; 58,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40,79; 59,82</t>
+          <t>41,69; 59,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64,44; 81,53</t>
+          <t>64,19; 81,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53,34; 76,59</t>
+          <t>53,28; 75,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>57,09; 79,87</t>
+          <t>56,84; 79,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,29; 87,79</t>
+          <t>66,86; 87,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,16; 61,87</t>
+          <t>48,75; 62,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,76; 64,69</t>
+          <t>49,59; 64,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>68,62; 82,65</t>
+          <t>69,05; 82,4</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>53,56; 61,24</t>
+          <t>53,85; 61,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>63,84; 70,74</t>
+          <t>63,91; 70,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56,27; 64,03</t>
+          <t>56,33; 63,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60,04; 72,34</t>
+          <t>60,06; 71,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>72,97; 81,47</t>
+          <t>73,32; 81,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>64,57; 74,64</t>
+          <t>65,07; 74,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>56,57; 63,1</t>
+          <t>56,47; 63,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>67,77; 73,22</t>
+          <t>67,98; 73,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>60,43; 66,62</t>
+          <t>60,28; 66,77</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20870; 33480</t>
+          <t>21165; 33809</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53948; 69120</t>
+          <t>54403; 69365</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51385; 66506</t>
+          <t>50820; 66910</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9337; 17941</t>
+          <t>8778; 17823</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25637; 36823</t>
+          <t>25480; 36575</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30807; 43626</t>
+          <t>31291; 44611</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33689; 48742</t>
+          <t>33293; 48935</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84271; 102872</t>
+          <t>84327; 103463</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>87260; 107624</t>
+          <t>87241; 106938</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53296; 74782</t>
+          <t>52761; 74441</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69449; 91564</t>
+          <t>68613; 91340</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29983; 47997</t>
+          <t>31985; 48794</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10611; 19994</t>
+          <t>9774; 20002</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45222; 55877</t>
+          <t>44970; 55742</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15819; 26094</t>
+          <t>16670; 26209</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67809; 90367</t>
+          <t>68335; 90914</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>118994; 145570</t>
+          <t>118341; 143564</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53424; 72157</t>
+          <t>51613; 71737</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32042; 47372</t>
+          <t>32092; 47656</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49846; 65431</t>
+          <t>49006; 65876</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25943; 41756</t>
+          <t>25263; 40730</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7359; 14236</t>
+          <t>7300; 13344</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18471; 28964</t>
+          <t>18844; 29013</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14288; 23839</t>
+          <t>15595; 23978</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42587; 59235</t>
+          <t>41784; 59063</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>72946; 91998</t>
+          <t>71337; 92273</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>43428; 61987</t>
+          <t>45162; 61261</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39943; 56921</t>
+          <t>39534; 56142</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64158; 83812</t>
+          <t>64794; 84594</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42013; 59758</t>
+          <t>41124; 59644</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16361; 28588</t>
+          <t>17187; 28912</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33604; 43631</t>
+          <t>33330; 43550</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19715; 32892</t>
+          <t>19749; 32909</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61197; 80777</t>
+          <t>61358; 82353</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>102544; 124161</t>
+          <t>102481; 124405</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65140; 88137</t>
+          <t>66179; 87932</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>27493; 37068</t>
+          <t>27532; 37007</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29242; 42844</t>
+          <t>29928; 43465</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12826; 24248</t>
+          <t>13422; 24580</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20786; 28133</t>
+          <t>21601; 28121</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12907; 22768</t>
+          <t>13485; 22664</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3528; 11575</t>
+          <t>3556; 11665</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>52539; 64179</t>
+          <t>51742; 63916</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>46282; 63077</t>
+          <t>46323; 63594</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19670; 33452</t>
+          <t>19184; 32878</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15982; 30702</t>
+          <t>15067; 29864</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>49761; 66567</t>
+          <t>50870; 67499</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25351; 37014</t>
+          <t>24751; 36590</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5102; 14513</t>
+          <t>6052; 14536</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11732; 20824</t>
+          <t>12762; 20839</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10311; 15989</t>
+          <t>10197; 16800</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24986; 41544</t>
+          <t>25009; 41468</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>67436; 86248</t>
+          <t>68066; 86433</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>37990; 51319</t>
+          <t>38158; 51295</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>43130; 62154</t>
+          <t>43202; 60963</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>97112; 122346</t>
+          <t>96949; 122287</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43005; 65170</t>
+          <t>43110; 64902</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12727; 24038</t>
+          <t>12877; 24173</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>58880; 76666</t>
+          <t>59166; 76177</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>46631; 64206</t>
+          <t>46359; 63684</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>60440; 82243</t>
+          <t>59776; 81410</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>164542; 194136</t>
+          <t>163426; 194505</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>95157; 125361</t>
+          <t>94119; 124579</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>57247; 81192</t>
+          <t>58246; 81593</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>53123; 77907</t>
+          <t>54290; 77630</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>65796; 83245</t>
+          <t>65541; 83293</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>38499; 55282</t>
+          <t>38455; 54760</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>38207; 53457</t>
+          <t>38042; 52960</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>42389; 56134</t>
+          <t>42752; 56154</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>101479; 130363</t>
+          <t>102703; 130860</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>98108; 127528</t>
+          <t>97774; 127250</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>113937; 137232</t>
+          <t>114654; 136817</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>334505; 382484</t>
+          <t>336313; 385026</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>520980; 577329</t>
+          <t>521546; 576324</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>340682; 387723</t>
+          <t>341105; 387069</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>150536; 181390</t>
+          <t>150598; 180176</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>282067; 314939</t>
+          <t>283419; 315071</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>216823; 250636</t>
+          <t>218497; 250987</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>495184; 552332</t>
+          <t>494299; 553554</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>815047; 880525</t>
+          <t>817611; 883544</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>568845; 627130</t>
+          <t>567445; 628504</t>
         </is>
       </c>
     </row>
